--- a/dataset/construct/dataset_splits/tum/fold2.xlsx
+++ b/dataset/construct/dataset_splits/tum/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AK54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>299</v>
+        <v>568</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,41 +625,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>75.3335159517834</v>
+        <v>80.78428017339721</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>36.3321799307958</v>
       </c>
       <c r="E2" t="n">
-        <v>28.4567901234567</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>229.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>233.3</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>398.5</v>
       </c>
       <c r="K2" t="n">
-        <v>455</v>
+        <v>861.6</v>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>118</v>
+        <v>7.6</v>
       </c>
       <c r="N2" t="n">
-        <v>629</v>
+        <v>46.3</v>
       </c>
       <c r="O2" t="n">
-        <v>130</v>
+        <v>53.9</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -683,40 +670,40 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>26.15</v>
       </c>
       <c r="V2" t="n">
-        <v>86</v>
+        <v>0.26</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>26.8334606569901</v>
       </c>
       <c r="X2" t="n">
-        <v>26.3</v>
+        <v>26.0709028381822</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.258278145695364</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>26.8406888888731</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -728,33 +715,24 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>212</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>472</v>
+        <v>528</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,85 +740,85 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>82.9967864793267</v>
+        <v>84.2009601490608</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>20.5498866213151</v>
       </c>
       <c r="E3" t="n">
-        <v>19.2276878705335</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>118.2</v>
       </c>
       <c r="I3" t="n">
-        <v>762</v>
+        <v>74.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>243</v>
+        <v>275</v>
       </c>
       <c r="L3" t="n">
-        <v>105</v>
+        <v>35.2</v>
       </c>
       <c r="M3" t="n">
-        <v>177</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>525</v>
+        <v>6.5</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>41.7</v>
       </c>
       <c r="P3" t="n">
-        <v>31.7</v>
+        <v>14.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>52.7</v>
+        <v>13.8</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="T3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
-        <v>12</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>22.8545963840081</v>
       </c>
       <c r="X3" t="n">
-        <v>20.45</v>
+        <v>22.0850401322991</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.140909090909091</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.1675579322638</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.6802165106906</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -849,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -861,24 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>72</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>184</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2583</v>
+        <v>2811</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,88 +855,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.0467322926965</v>
+        <v>83.34377059725711</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>28.344671201814</v>
       </c>
       <c r="E4" t="n">
-        <v>26.2975778546712</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>389</v>
       </c>
       <c r="I4" t="n">
-        <v>1320</v>
+        <v>304</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>960</v>
       </c>
       <c r="L4" t="n">
-        <v>401</v>
+        <v>177</v>
       </c>
       <c r="M4" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1383</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="P4" t="n">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="Q4" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>7</v>
+        <v>24.05</v>
       </c>
       <c r="V4" t="n">
-        <v>7</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>24.3188184364655</v>
       </c>
       <c r="X4" t="n">
-        <v>24.65</v>
+        <v>23.9592772737234</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.220216606498195</v>
+        <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>24.8281130634072</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>24.3439993862133</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -976,7 +945,7 @@
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
@@ -985,24 +954,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>154</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>493</v>
+        <v>598</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1010,121 +970,114 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>86.04058293406339</v>
+        <v>80.29658529165719</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>17.0068027210884</v>
       </c>
       <c r="E5" t="n">
-        <v>24.765625</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="I5" t="n">
-        <v>668</v>
+        <v>129</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>77</v>
       </c>
       <c r="K5" t="n">
-        <v>978</v>
+        <v>238</v>
       </c>
       <c r="L5" t="n">
-        <v>246</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="N5" t="n">
-        <v>1512</v>
+        <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="P5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>139</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>37</v>
+        <v>19.8</v>
       </c>
       <c r="V5" t="n">
-        <v>37</v>
+        <v>0.29</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>19.7351667939903</v>
       </c>
       <c r="X5" t="n">
-        <v>22.8</v>
+        <v>19.1461601132455</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.323529411764706</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.2683982683983</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>23.1211849536588</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>368</v>
+        <v>464</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1132,77 +1085,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>74.1969855755824</v>
+        <v>88.22278655537809</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E6" t="n">
-        <v>26.0261748958953</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>490</v>
+      </c>
+      <c r="I6" t="n">
+        <v>661</v>
+      </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>651</v>
       </c>
       <c r="K6" t="n">
-        <v>1100</v>
+        <v>1802</v>
       </c>
       <c r="L6" t="n">
-        <v>297</v>
+        <v>129</v>
       </c>
       <c r="M6" t="n">
-        <v>260</v>
+        <v>228</v>
       </c>
       <c r="N6" t="n">
-        <v>1657</v>
+        <v>183</v>
       </c>
       <c r="O6" t="n">
-        <v>33</v>
+        <v>540</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q6" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="R6" t="n">
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>163</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>20.690094219506</v>
       </c>
       <c r="X6" t="n">
-        <v>22.35</v>
+        <v>20.4636637734958</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.226190476190476</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.3940969210825</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1217,36 +1172,27 @@
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>124</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1345</v>
+        <v>465</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1254,88 +1200,88 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>77.4494138971278</v>
+        <v>84.6639147146805</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>30.1204819277108</v>
       </c>
       <c r="E7" t="n">
-        <v>24.3374797187669</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>706</v>
       </c>
       <c r="I7" t="n">
-        <v>5850</v>
+        <v>610</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>269</v>
       </c>
       <c r="K7" t="n">
-        <v>40.4</v>
+        <v>1585</v>
       </c>
       <c r="L7" t="n">
-        <v>36.5</v>
+        <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>7.6</v>
+        <v>107</v>
       </c>
       <c r="N7" t="n">
-        <v>84.5</v>
+        <v>12</v>
       </c>
       <c r="O7" t="n">
-        <v>4.7</v>
+        <v>168</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>25.55</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X7" t="n">
-        <v>23.7</v>
+        <v>25.327989110736</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.211320754716981</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>23.8413547237077</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>23.506086798771</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1353,22 +1299,15 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>178</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>603</v>
+        <v>557</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1376,79 +1315,79 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>77.0139021978858</v>
+        <v>91.0891873906761</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>29.3575219240468</v>
       </c>
       <c r="E8" t="n">
-        <v>37.2536452491587</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>60</v>
+        <v>11.9</v>
       </c>
       <c r="I8" t="n">
-        <v>909</v>
+        <v>30.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>170.9</v>
       </c>
       <c r="K8" t="n">
-        <v>656</v>
+        <v>213.4</v>
       </c>
       <c r="L8" t="n">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>1401</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>96</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>193</v>
+        <v>62.7</v>
       </c>
       <c r="S8" t="n">
-        <v>46</v>
+        <v>62.7</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="V8" t="n">
-        <v>46</v>
+        <v>0.22</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>22.1224853577795</v>
       </c>
       <c r="X8" t="n">
-        <v>24.9</v>
+        <v>21.8532914302955</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.148698884758364</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>26.1013496307614</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>25.0246489572143</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1466,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
@@ -1475,24 +1414,13 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>170</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>899</v>
+        <v>597</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1500,91 +1428,91 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>80.2974793076787</v>
+        <v>80.8852175070348</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>24.9680097375237</v>
       </c>
       <c r="E9" t="n">
-        <v>27.7769298861451</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>532</v>
       </c>
       <c r="I9" t="n">
-        <v>514</v>
+        <v>615</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>593</v>
       </c>
       <c r="K9" t="n">
-        <v>407</v>
+        <v>1740</v>
       </c>
       <c r="L9" t="n">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="M9" t="n">
-        <v>304</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>919</v>
+        <v>18</v>
       </c>
       <c r="O9" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="P9" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>8</v>
+        <v>28.1</v>
       </c>
       <c r="V9" t="n">
-        <v>8</v>
+        <v>0.19</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>28.6478227654698</v>
       </c>
       <c r="X9" t="n">
-        <v>27.05</v>
+        <v>27.9784080907002</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.260450160771704</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>27.6928953399542</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>26.9117274486368</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1599,24 +1527,13 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>138</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>160</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>495</v>
+        <v>577</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1624,85 +1541,85 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>74.7334821722818</v>
+        <v>85.0743345501559</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>25.5593291551416</v>
       </c>
       <c r="E10" t="n">
-        <v>30.1102788964582</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
+        <v>903.7</v>
       </c>
       <c r="I10" t="n">
-        <v>461</v>
+        <v>809.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>747.3</v>
       </c>
       <c r="K10" t="n">
-        <v>575</v>
+        <v>2460.6</v>
       </c>
       <c r="L10" t="n">
-        <v>273</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>224</v>
+        <v>58.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1072</v>
+        <v>146.1</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>211.1</v>
       </c>
       <c r="P10" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>29</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="R10" t="n">
-        <v>105</v>
+        <v>63.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>72.7</v>
       </c>
       <c r="T10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="V10" t="n">
-        <v>18</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>24.7962821492233</v>
       </c>
       <c r="X10" t="n">
-        <v>24.35</v>
+        <v>24.4717629124263</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.15530303030303</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>23.7726133940886</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1711,10 +1628,10 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -1723,24 +1640,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>352</v>
+        <v>2319</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1748,77 +1656,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>89.8024340254012</v>
+        <v>77.2493207024615</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>28.515625</v>
       </c>
       <c r="E11" t="n">
-        <v>27.34375</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>35</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
+        <v>55.8</v>
+      </c>
+      <c r="I11" t="n">
+        <v>46.7</v>
+      </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>14.9</v>
       </c>
       <c r="K11" t="n">
-        <v>325</v>
+        <v>117.4</v>
       </c>
       <c r="L11" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>654</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>8</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X11" t="n">
-        <v>21.9</v>
+        <v>22.1741916431478</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.315384615384615</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.5999490705373</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.7511249453965</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1827,7 +1737,7 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1845,24 +1755,15 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2006</v>
+        <v>487</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1870,91 +1771,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>67.10314342662311</v>
+        <v>86.317406900398</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>16.5051903114186</v>
       </c>
       <c r="E12" t="n">
-        <v>33.8123415046491</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
+        <v>772</v>
       </c>
       <c r="I12" t="n">
-        <v>391</v>
+        <v>150</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>244</v>
       </c>
       <c r="K12" t="n">
-        <v>718.6</v>
+        <v>1166</v>
       </c>
       <c r="L12" t="n">
-        <v>1023.4</v>
+        <v>180</v>
       </c>
       <c r="M12" t="n">
-        <v>535.8</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2277.8</v>
+        <v>43</v>
       </c>
       <c r="O12" t="n">
-        <v>52</v>
+        <v>223</v>
       </c>
       <c r="P12" t="n">
-        <v>140.7</v>
+        <v>158</v>
       </c>
       <c r="Q12" t="n">
-        <v>59.7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>252.4</v>
+        <v>24</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>182</v>
       </c>
       <c r="T12" t="n">
-        <v>100.6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>5</v>
+        <v>25.45</v>
       </c>
       <c r="V12" t="n">
-        <v>105.6</v>
+        <v>0.32</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>27.1836007130125</v>
       </c>
       <c r="X12" t="n">
-        <v>27.2</v>
+        <v>26.0709028381822</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0912280701754387</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>27.6610644257703</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>27.3480481672903</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1969,24 +1870,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>92</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>226</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>801</v>
+        <v>458</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1994,88 +1886,88 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>77.94204359647119</v>
+        <v>87.1275439196897</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>24.9770431588613</v>
       </c>
       <c r="E13" t="n">
-        <v>35.546875</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
+        <v>746</v>
       </c>
       <c r="I13" t="n">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>797</v>
       </c>
       <c r="K13" t="n">
-        <v>838</v>
+        <v>2275</v>
       </c>
       <c r="L13" t="n">
-        <v>779</v>
+        <v>120</v>
       </c>
       <c r="M13" t="n">
-        <v>674</v>
+        <v>135</v>
       </c>
       <c r="N13" t="n">
-        <v>2291</v>
+        <v>231</v>
       </c>
       <c r="O13" t="n">
-        <v>83</v>
+        <v>486</v>
       </c>
       <c r="P13" t="n">
-        <v>265</v>
+        <v>44</v>
       </c>
       <c r="Q13" t="n">
-        <v>146</v>
+        <v>32</v>
       </c>
       <c r="R13" t="n">
-        <v>494</v>
+        <v>209</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="T13" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>176</v>
+        <v>25.55</v>
       </c>
       <c r="V13" t="n">
-        <v>232</v>
+        <v>0.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>25.9421950598421</v>
       </c>
       <c r="X13" t="n">
-        <v>22.55</v>
+        <v>25.4282983710565</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.105042016806723</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>22.5921534344381</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2084,33 +1976,24 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2513</v>
+        <v>983</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2118,82 +2001,82 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>84.37595016731311</v>
+        <v>74.1668630694349</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>25.4580659041199</v>
       </c>
       <c r="E14" t="n">
-        <v>24.6755002704164</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>40</v>
+        <v>993</v>
       </c>
       <c r="I14" t="n">
-        <v>17600</v>
+        <v>491</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>960</v>
       </c>
       <c r="K14" t="n">
-        <v>392.4</v>
+        <v>2444</v>
       </c>
       <c r="L14" t="n">
-        <v>407.3</v>
+        <v>227</v>
       </c>
       <c r="M14" t="n">
-        <v>215.7</v>
+        <v>100</v>
       </c>
       <c r="N14" t="n">
-        <v>1015.4</v>
+        <v>43</v>
       </c>
       <c r="O14" t="n">
-        <v>52.4</v>
+        <v>370</v>
       </c>
       <c r="P14" t="n">
-        <v>28.3</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="R14" t="n">
-        <v>80.7</v>
+        <v>17</v>
       </c>
       <c r="S14" t="n">
-        <v>24.1</v>
+        <v>206</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V14" t="n">
-        <v>24.1</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X14" t="n">
-        <v>25.53</v>
+        <v>23.6921643870788</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.199576868829337</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.305576776165</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>25.0017500819378</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2205,10 +2088,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2217,24 +2100,15 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>246</v>
+        <v>118</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2242,43 +2116,43 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.25305355920599</v>
+        <v>91.0289564795802</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>23.1111111111111</v>
       </c>
       <c r="E15" t="n">
-        <v>20.8325296091971</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>396</v>
       </c>
       <c r="I15" t="n">
-        <v>209</v>
+        <v>148</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>307</v>
       </c>
       <c r="K15" t="n">
-        <v>877</v>
+        <v>851</v>
       </c>
       <c r="L15" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="M15" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="N15" t="n">
-        <v>1071</v>
+        <v>66</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
@@ -2287,34 +2161,34 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>20.05</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X15" t="n">
-        <v>23.9</v>
+        <v>19.8319163664306</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.249084249084249</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>24.1914947797301</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.5574721962474</v>
+        <v>1</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2338,27 +2212,18 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>188</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>500</v>
+        <v>601</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2366,85 +2231,85 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>71.47246748802191</v>
+        <v>88.0775420184044</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>22.9004724889498</v>
       </c>
       <c r="E16" t="n">
-        <v>24.1671624033313</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>764</v>
       </c>
       <c r="I16" t="n">
-        <v>587</v>
+        <v>756</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>552</v>
       </c>
       <c r="K16" t="n">
-        <v>168.7</v>
+        <v>2072</v>
       </c>
       <c r="L16" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="M16" t="n">
-        <v>128.9</v>
+        <v>75</v>
       </c>
       <c r="N16" t="n">
-        <v>380.6</v>
+        <v>78</v>
       </c>
       <c r="O16" t="n">
-        <v>23.7</v>
+        <v>246</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q16" t="n">
-        <v>12.6</v>
+        <v>10</v>
       </c>
       <c r="R16" t="n">
-        <v>36.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>8</v>
+        <v>23.15</v>
       </c>
       <c r="V16" t="n">
-        <v>8</v>
+        <v>0.28</v>
       </c>
       <c r="W16" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X16" t="n">
-        <v>25.15</v>
+        <v>22.9831467948561</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.277397260273973</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>25.3692386045327</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>24.7150115381059</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2459,28 +2324,21 @@
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>93</v>
-      </c>
-      <c r="AN16" t="inlineStr"/>
+        <v>128</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>959</v>
+        <v>1997</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2488,79 +2346,79 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>75.6452314814815</v>
+        <v>80.8359181940325</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>23.309053069719</v>
       </c>
       <c r="E17" t="n">
-        <v>19.9510204081632</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>60</v>
+        <v>91.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5050</v>
+        <v>81.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>52.5</v>
       </c>
       <c r="K17" t="n">
-        <v>281</v>
+        <v>226</v>
       </c>
       <c r="L17" t="n">
-        <v>78</v>
+        <v>18.2</v>
       </c>
       <c r="M17" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>394</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>10</v>
+        <v>18.2</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W17" t="n">
-        <v>2</v>
+        <v>22.0588235294118</v>
       </c>
       <c r="X17" t="n">
-        <v>22.4</v>
+        <v>21.710123730909</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.283524904214559</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.6203056614775</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2575,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2587,22 +2445,15 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>126</v>
-      </c>
-      <c r="AN17" t="inlineStr"/>
+        <v>154</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>306</v>
+        <v>546</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2610,44 +2461,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>82.1829412566228</v>
+        <v>83.8833922731767</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>33.0904223676383</v>
       </c>
       <c r="E18" t="n">
-        <v>21.2305720237141</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
         <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="I18" t="n">
+        <v>29</v>
+      </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>188</v>
       </c>
       <c r="K18" t="n">
-        <v>70</v>
+        <v>422</v>
       </c>
       <c r="L18" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M18" t="n">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -2656,31 +2509,31 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>22.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>22.9182582123759</v>
       </c>
       <c r="X18" t="n">
-        <v>22.8</v>
+        <v>21.7452723622298</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.323529411764706</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.8721164508225</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -2695,32 +2548,25 @@
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
+        <v>128</v>
+      </c>
+      <c r="AK18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1870</v>
+        <v>2013</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2728,88 +2574,88 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>75.305613449692</v>
+        <v>92.0309740284432</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>26.7949380165289</v>
       </c>
       <c r="E19" t="n">
-        <v>28.3059950645957</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>60</v>
+        <v>262.3</v>
       </c>
       <c r="I19" t="n">
-        <v>482</v>
+        <v>377.1</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>280.3</v>
       </c>
       <c r="K19" t="n">
-        <v>203.8</v>
+        <v>919.7</v>
       </c>
       <c r="L19" t="n">
-        <v>177.1</v>
+        <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>101.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>482.2</v>
+        <v>29.1</v>
       </c>
       <c r="O19" t="n">
-        <v>14.5</v>
+        <v>36.7</v>
       </c>
       <c r="P19" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>40.9</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>10.3</v>
+        <v>24.6</v>
       </c>
       <c r="V19" t="n">
-        <v>10.3</v>
+        <v>0.12</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>24.5098039215686</v>
       </c>
       <c r="X19" t="n">
-        <v>22.45</v>
+        <v>26.4561900936673</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.23921568627451</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.7591036414566</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.6661077559205</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
@@ -2824,23 +2670,12 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>166</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2855,83 +2690,85 @@
         <v>79.7188668339798</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>28.0403781445281</v>
       </c>
       <c r="E20" t="n">
-        <v>28.0403781445281</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>55</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
+        <v>209</v>
+      </c>
+      <c r="I20" t="n">
+        <v>137.7</v>
+      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>85</v>
       </c>
       <c r="K20" t="n">
-        <v>209</v>
+        <v>431.7</v>
       </c>
       <c r="L20" t="n">
-        <v>137.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>431.7</v>
+        <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>50</v>
+        <v>22.1</v>
       </c>
       <c r="V20" t="n">
-        <v>50</v>
+        <v>0.35</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X20" t="n">
-        <v>22.1</v>
+        <v>21.406057760656</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.350746268656717</v>
+        <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.5999490705373</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.406057760656</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2940,33 +2777,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>103</v>
-      </c>
-      <c r="AN20" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>512</v>
+        <v>544</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2974,79 +2802,79 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>85.7615408015819</v>
+        <v>86.9331313534616</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>29.5525494276795</v>
       </c>
       <c r="E21" t="n">
-        <v>25.9106843468983</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>60</v>
+        <v>256</v>
       </c>
       <c r="I21" t="n">
-        <v>8040</v>
+        <v>186</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="K21" t="n">
-        <v>248</v>
+        <v>476</v>
       </c>
       <c r="L21" t="n">
-        <v>269</v>
+        <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="N21" t="n">
-        <v>615</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="P21" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>21.75</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X21" t="n">
-        <v>22.8</v>
+        <v>21.3763064498772</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.323529411764706</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>23.554876496053</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.7045529015462</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3061,34 +2889,27 @@
         <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN21" t="inlineStr"/>
+        <v>208</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1962</v>
+        <v>585</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3096,79 +2917,79 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>74.1123504322255</v>
+        <v>75.1550840368089</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>27.1706315662359</v>
       </c>
       <c r="E22" t="n">
-        <v>25.0593070266296</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>331</v>
       </c>
       <c r="I22" t="n">
-        <v>35000</v>
+        <v>96</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="K22" t="n">
-        <v>783.1</v>
+        <v>699</v>
       </c>
       <c r="L22" t="n">
-        <v>744.9</v>
+        <v>46</v>
       </c>
       <c r="M22" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>1697</v>
+        <v>75</v>
       </c>
       <c r="O22" t="n">
-        <v>0.4</v>
+        <v>121</v>
       </c>
       <c r="P22" t="n">
-        <v>196.2</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>196.6</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>92.3</v>
+        <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="V22" t="n">
-        <v>92.3</v>
+        <v>0.43</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>28.4250063661828</v>
       </c>
       <c r="X22" t="n">
-        <v>28.15</v>
+        <v>26.6503269908915</v>
       </c>
       <c r="Y22" t="n">
-        <v>0.19551282051282</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>28.5841609371021</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>28.1846427181971</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3177,10 +2998,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3195,24 +3016,13 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>142</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>156</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2012</v>
+        <v>2513</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3220,86 +3030,88 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>84.8005503270211</v>
+        <v>84.37595016731311</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>24.6755002704164</v>
       </c>
       <c r="E23" t="n">
-        <v>25.5102040816326</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
-      </c>
-      <c r="I23" t="inlineStr"/>
+        <v>392.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>407.3</v>
+      </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>215.7</v>
       </c>
       <c r="K23" t="n">
-        <v>564.9</v>
+        <v>1015.4</v>
       </c>
       <c r="L23" t="n">
-        <v>316.7</v>
+        <v>52.4</v>
       </c>
       <c r="M23" t="n">
-        <v>120.3</v>
+        <v>28.3</v>
       </c>
       <c r="N23" t="n">
-        <v>1001.9</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>94.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="P23" t="n">
-        <v>6.6</v>
+        <v>24.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>116.3</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>24.1</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>25.53</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X23" t="n">
-        <v>24.85</v>
+        <v>25.0017500819378</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.348837209302326</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>25.9103641456583</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>24.8126692377086</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3308,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
@@ -3317,24 +3129,15 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>174</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>620</v>
+        <v>642</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3342,88 +3145,88 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>85.82740633001239</v>
+        <v>85.4307209673739</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>34.0866052266128</v>
       </c>
       <c r="E24" t="n">
-        <v>29.0659268067115</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
+        <v>174</v>
       </c>
       <c r="I24" t="n">
-        <v>728</v>
+        <v>257</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>135</v>
       </c>
       <c r="K24" t="n">
-        <v>1675</v>
+        <v>566</v>
       </c>
       <c r="L24" t="n">
-        <v>1134</v>
+        <v>37</v>
       </c>
       <c r="M24" t="n">
-        <v>1007</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3816</v>
+        <v>11</v>
       </c>
       <c r="O24" t="n">
-        <v>371</v>
+        <v>48</v>
       </c>
       <c r="P24" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>811</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>191</v>
+        <v>26.1</v>
       </c>
       <c r="V24" t="n">
-        <v>358</v>
+        <v>0.28</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>26.6424751718869</v>
       </c>
       <c r="X24" t="n">
-        <v>26.4</v>
+        <v>25.9240233435526</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.160278745644599</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>26.4196587726</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>26.3138801572997</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
@@ -3441,24 +3244,13 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>230</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>655</v>
+        <v>634</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3466,83 +3258,85 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>88.7510476081831</v>
+        <v>85.36462278500269</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>30.4271978579252</v>
       </c>
       <c r="E25" t="n">
-        <v>20.9366391184573</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>38</v>
-      </c>
-      <c r="I25" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="I25" t="n">
+        <v>26.4</v>
+      </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>217</v>
+        <v>104.4</v>
       </c>
       <c r="L25" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>404</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>22.9</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W25" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X25" t="n">
-        <v>22</v>
+        <v>22.6736985933985</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.333333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.440794499618</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.7599008686688</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3551,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -3563,22 +3357,15 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>146</v>
-      </c>
-      <c r="AN25" t="inlineStr"/>
+        <v>186</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1314</v>
+        <v>1003</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3586,85 +3373,85 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>79.1469129464852</v>
+        <v>74.4512648300251</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>30.6689049586776</v>
       </c>
       <c r="E26" t="n">
-        <v>31.833910034602</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G26" t="n">
         <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>50</v>
+        <v>309</v>
       </c>
       <c r="I26" t="n">
-        <v>1150</v>
+        <v>249</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
       <c r="K26" t="n">
-        <v>120.5</v>
+        <v>668</v>
       </c>
       <c r="L26" t="n">
-        <v>175.9</v>
+        <v>20</v>
       </c>
       <c r="M26" t="n">
-        <v>229.1</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>525.5</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
-        <v>35.9</v>
+        <v>71</v>
       </c>
       <c r="P26" t="n">
-        <v>28.7</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>92.09999999999999</v>
+        <v>19</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>25.05</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X26" t="n">
-        <v>23</v>
+        <v>24.1971578951015</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.270676691729323</v>
+        <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>24.2869875222816</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.3675988578761</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3673,10 +3460,10 @@
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3685,22 +3472,15 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>106</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>300</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2010</v>
+        <v>2868</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3708,79 +3488,79 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>84.44497680431969</v>
+        <v>79.58796220244891</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>23.4375</v>
       </c>
       <c r="E27" t="n">
-        <v>23.0111768573307</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>718</v>
       </c>
       <c r="I27" t="n">
-        <v>1520</v>
+        <v>370</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="K27" t="n">
-        <v>30.6</v>
+        <v>1444</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>11.1</v>
+        <v>27</v>
       </c>
       <c r="N27" t="n">
-        <v>41.7</v>
+        <v>127</v>
       </c>
       <c r="O27" t="n">
-        <v>24.5</v>
+        <v>165</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="R27" t="n">
-        <v>24.5</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>45.5</v>
+        <v>9</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="V27" t="n">
-        <v>45.5</v>
+        <v>0.24</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>23.3638910109498</v>
       </c>
       <c r="X27" t="n">
-        <v>19.35</v>
+        <v>22.8359153550381</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.208333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.4805194805195</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>19.1826891138042</v>
+        <v>1</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -3792,7 +3572,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -3807,24 +3587,13 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>178</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="AK27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>597</v>
+        <v>481</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3832,79 +3601,79 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>80.8852175070348</v>
+        <v>88.08028322812891</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>23.5078053259871</v>
       </c>
       <c r="E28" t="n">
-        <v>24.9680097375237</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>29</v>
+        <v>726</v>
       </c>
       <c r="I28" t="n">
-        <v>1360</v>
+        <v>396</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>285</v>
       </c>
       <c r="K28" t="n">
-        <v>532</v>
+        <v>1407</v>
       </c>
       <c r="L28" t="n">
-        <v>615</v>
+        <v>104</v>
       </c>
       <c r="M28" t="n">
-        <v>593</v>
+        <v>23</v>
       </c>
       <c r="N28" t="n">
-        <v>1740</v>
+        <v>38</v>
       </c>
       <c r="O28" t="n">
-        <v>35</v>
+        <v>165</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="R28" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>22.55</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X28" t="n">
-        <v>28.1</v>
+        <v>21.6131702613684</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.187096774193548</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>28.6478227654698</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>27.9784080907002</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3931,22 +3700,15 @@
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN28" t="inlineStr"/>
+        <v>190</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1720</v>
+        <v>2636</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3954,77 +3716,79 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>68.3052995474941</v>
+        <v>85.0193633229396</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>27.1314117909923</v>
       </c>
       <c r="E29" t="n">
-        <v>30.7173999207292</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>60</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>560</v>
+      </c>
+      <c r="I29" t="n">
+        <v>472</v>
+      </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>603</v>
       </c>
       <c r="K29" t="n">
-        <v>166.7</v>
+        <v>1635</v>
       </c>
       <c r="L29" t="n">
-        <v>262</v>
+        <v>15</v>
       </c>
       <c r="M29" t="n">
-        <v>248</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>676.7</v>
+        <v>49</v>
       </c>
       <c r="O29" t="n">
-        <v>44.4</v>
+        <v>69</v>
       </c>
       <c r="P29" t="n">
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>95.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>139.6</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>23.3</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>99.8</v>
+        <v>28.4</v>
       </c>
       <c r="V29" t="n">
-        <v>123.1</v>
+        <v>0.23</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>27.8838808250573</v>
       </c>
       <c r="X29" t="n">
-        <v>24.25</v>
+        <v>27.2524701589629</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.286219081272085</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>23.0936433298824</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4036,39 +3800,30 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="AK29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>174</v>
+        <v>210</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2158</v>
+        <v>1315</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4076,77 +3831,79 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>88.0696089056202</v>
+        <v>77.34847025756081</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>29.0687732977668</v>
       </c>
       <c r="E30" t="n">
-        <v>29.3877551020408</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>45</v>
-      </c>
-      <c r="I30" t="inlineStr"/>
+        <v>645.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>346.9</v>
+      </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>419.5</v>
       </c>
       <c r="K30" t="n">
-        <v>157.2</v>
+        <v>1412.3</v>
       </c>
       <c r="L30" t="n">
-        <v>177.4</v>
+        <v>73</v>
       </c>
       <c r="M30" t="n">
-        <v>280.7</v>
+        <v>18</v>
       </c>
       <c r="N30" t="n">
-        <v>615.3</v>
+        <v>7.6</v>
       </c>
       <c r="O30" t="n">
-        <v>64.2</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="Q30" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>22.6</v>
+        <v>26.8</v>
       </c>
       <c r="V30" t="n">
-        <v>22.6</v>
+        <v>0.21</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>27.6292335115865</v>
       </c>
       <c r="X30" t="n">
-        <v>27.9</v>
+        <v>26.9920118011893</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.293577981651376</v>
+        <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>28.615991851286</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>27.2921406849679</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4155,10 +3912,10 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4173,18 +3930,11 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>125</v>
-      </c>
-      <c r="AN30" t="inlineStr"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4199,120 +3949,111 @@
         <v>84.6962753821583</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>24.5351239669421</v>
       </c>
       <c r="E31" t="n">
-        <v>24.5351239669421</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>45</v>
+        <v>739</v>
       </c>
       <c r="I31" t="n">
-        <v>3590</v>
+        <v>570</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>485</v>
       </c>
       <c r="K31" t="n">
-        <v>739</v>
+        <v>1794</v>
       </c>
       <c r="L31" t="n">
-        <v>570</v>
+        <v>90</v>
       </c>
       <c r="M31" t="n">
-        <v>485</v>
+        <v>69</v>
       </c>
       <c r="N31" t="n">
-        <v>1794</v>
+        <v>35</v>
       </c>
       <c r="O31" t="n">
+        <v>194</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>29.85</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="W31" t="n">
+        <v>29.921059332824</v>
+      </c>
+      <c r="X31" t="n">
+        <v>28.8077434310377</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
         <v>90</v>
       </c>
-      <c r="P31" t="n">
-        <v>69</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>35</v>
-      </c>
-      <c r="R31" t="n">
-        <v>194</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>29.85</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0.313559322033898</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>29.921059332824</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>28.8077434310377</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN31" t="n">
         <v>180</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1147</v>
+        <v>954</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4320,85 +4061,85 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>77.6437583656552</v>
+        <v>78.7770593771389</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>28.2283864654296</v>
       </c>
       <c r="E32" t="n">
-        <v>35.7559561895442</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
+        <v>488</v>
       </c>
       <c r="I32" t="n">
-        <v>673</v>
+        <v>578</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
       <c r="K32" t="n">
-        <v>60</v>
+        <v>1452</v>
       </c>
       <c r="L32" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="M32" t="n">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="N32" t="n">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="P32" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>23.05</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X32" t="n">
-        <v>21.35</v>
+        <v>22.8163986665956</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.15948275862069</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>21.3267125031831</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>21.1969216859002</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4419,24 +4160,15 @@
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>90</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>642</v>
+        <v>574</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4444,85 +4176,85 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>85.4307209673739</v>
+        <v>78.2242470910335</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>22.151022507021</v>
       </c>
       <c r="E33" t="n">
-        <v>34.0866052266128</v>
+        <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
         <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="I33" t="n">
-        <v>2910</v>
+        <v>278</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>181.2</v>
       </c>
       <c r="K33" t="n">
-        <v>174</v>
+        <v>827.2</v>
       </c>
       <c r="L33" t="n">
-        <v>257</v>
+        <v>28.9</v>
       </c>
       <c r="M33" t="n">
-        <v>135</v>
+        <v>6.9</v>
       </c>
       <c r="N33" t="n">
-        <v>566</v>
+        <v>61</v>
       </c>
       <c r="O33" t="n">
-        <v>37</v>
+        <v>96.8</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>48</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>22.4</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>22.5362872421696</v>
       </c>
       <c r="X33" t="n">
-        <v>26.1</v>
+        <v>22.1627083737899</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.277227722772277</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>26.6424751718869</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>25.9240233435526</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4531,10 +4263,10 @@
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
@@ -4543,22 +4275,13 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN33" t="inlineStr"/>
+        <v>80</v>
+      </c>
+      <c r="AK33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>611</v>
+        <v>552</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4566,119 +4289,114 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>86.12057761046469</v>
+        <v>84.7838999163434</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>21.4532871972318</v>
       </c>
       <c r="E34" t="n">
-        <v>25.390625</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>51</v>
-      </c>
-      <c r="I34" t="inlineStr"/>
+        <v>158</v>
+      </c>
+      <c r="I34" t="n">
+        <v>138</v>
+      </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>87</v>
       </c>
       <c r="K34" t="n">
-        <v>431</v>
+        <v>383</v>
       </c>
       <c r="L34" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>648</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>147</v>
+        <v>8</v>
       </c>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="V34" t="n">
-        <v>13</v>
+        <v>0.25</v>
       </c>
       <c r="W34" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X34" t="n">
-        <v>22.9</v>
+        <v>20.307569474639</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.284644194756554</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>23.6822001527884</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>22.5639660829322</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN34" t="inlineStr"/>
+        <v>162</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>452</v>
+        <v>1427</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4686,85 +4404,85 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>75.6426521345096</v>
+        <v>86.99098473901689</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>25.2080856123662</v>
       </c>
       <c r="E35" t="n">
-        <v>31.4359113034072</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>60</v>
+        <v>319.5</v>
       </c>
       <c r="I35" t="n">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>264.3</v>
       </c>
       <c r="K35" t="n">
-        <v>679</v>
+        <v>786.8</v>
       </c>
       <c r="L35" t="n">
-        <v>324</v>
+        <v>36.6</v>
       </c>
       <c r="M35" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1087</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>18.7</v>
+        <v>36.6</v>
       </c>
       <c r="P35" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>45.7</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>22.35</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>23.0137509549274</v>
       </c>
       <c r="X35" t="n">
-        <v>24.3</v>
+        <v>22.1512191514658</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.258064516129032</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
-        <v>24.0641711229947</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>23.2857506244092</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -4776,7 +4494,7 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
@@ -4785,24 +4503,15 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>914</v>
+        <v>681</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4810,79 +4519,79 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>84.0671732958146</v>
+        <v>74.1720111795574</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>25.9515570934256</v>
       </c>
       <c r="E36" t="n">
-        <v>25.7629805786761</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
-        <v>60</v>
+        <v>190</v>
       </c>
       <c r="I36" t="n">
-        <v>1400</v>
+        <v>215</v>
       </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>152</v>
       </c>
       <c r="K36" t="n">
-        <v>855</v>
+        <v>557</v>
       </c>
       <c r="L36" t="n">
-        <v>534</v>
+        <v>57</v>
       </c>
       <c r="M36" t="n">
-        <v>428</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1817</v>
+        <v>11</v>
       </c>
       <c r="O36" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="P36" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="Q36" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>93</v>
+        <v>22.9</v>
       </c>
       <c r="V36" t="n">
-        <v>93</v>
+        <v>0.2</v>
       </c>
       <c r="W36" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X36" t="n">
-        <v>29</v>
+        <v>22.3940969210825</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.220858895705522</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>29.921059332824</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>29.2679951700071</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
@@ -4909,22 +4618,15 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>154</v>
-      </c>
-      <c r="AN36" t="inlineStr"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1698</v>
+        <v>2158</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4932,89 +4634,91 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>87.9844727735949</v>
+        <v>88.0696089056202</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>29.3877551020408</v>
       </c>
       <c r="E37" t="n">
-        <v>30.1160023795359</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>157.2</v>
+      </c>
+      <c r="I37" t="n">
+        <v>177.4</v>
+      </c>
       <c r="J37" t="n">
-        <v>1</v>
+        <v>280.7</v>
       </c>
       <c r="K37" t="n">
-        <v>282</v>
+        <v>615.3</v>
       </c>
       <c r="L37" t="n">
-        <v>487</v>
+        <v>64.2</v>
       </c>
       <c r="M37" t="n">
-        <v>571</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1340</v>
+        <v>52.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="P37" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>234</v>
+        <v>22.6</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>22.6</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>28.615991851286</v>
       </c>
       <c r="X37" t="n">
-        <v>27.35</v>
+        <v>27.2921406849679</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.218241042345277</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>28.3295136236313</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>27.6120628833503</v>
+        <v>1</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5029,24 +4733,13 @@
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>284</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="AK37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1079</v>
+        <v>1265</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5054,85 +4747,85 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>88.0231582249601</v>
+        <v>52.5566858379598</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>20.0065693212696</v>
       </c>
       <c r="E38" t="n">
-        <v>24.2809753428405</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>60</v>
+        <v>328</v>
       </c>
       <c r="I38" t="n">
-        <v>928</v>
+        <v>242</v>
       </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>345</v>
       </c>
       <c r="K38" t="n">
-        <v>800</v>
+        <v>915</v>
       </c>
       <c r="L38" t="n">
-        <v>544</v>
+        <v>183</v>
       </c>
       <c r="M38" t="n">
-        <v>439</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1783</v>
+        <v>156</v>
       </c>
       <c r="O38" t="n">
-        <v>15</v>
+        <v>339</v>
       </c>
       <c r="P38" t="n">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>335</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>25.45</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W38" t="n">
-        <v>1</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X38" t="n">
-        <v>23.3</v>
+        <v>25.2524956816771</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.299270072992701</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>22.9182582123759</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>22.050433101168</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5144,33 +4837,24 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>170</v>
+        <v>132</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2847</v>
+        <v>1870</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5178,79 +4862,79 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>83.10646231018831</v>
+        <v>75.305613449692</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>28.3059950645957</v>
       </c>
       <c r="E39" t="n">
-        <v>29.8649584487534</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G39" t="n">
         <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
+        <v>203.8</v>
       </c>
       <c r="I39" t="n">
-        <v>35000</v>
+        <v>177.1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>101.3</v>
       </c>
       <c r="K39" t="n">
-        <v>156</v>
+        <v>482.2</v>
       </c>
       <c r="L39" t="n">
-        <v>197</v>
+        <v>14.5</v>
       </c>
       <c r="M39" t="n">
-        <v>235</v>
+        <v>13.4</v>
       </c>
       <c r="N39" t="n">
-        <v>588</v>
+        <v>13</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>40.9</v>
       </c>
       <c r="P39" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>292</v>
+        <v>10.3</v>
       </c>
       <c r="S39" t="n">
-        <v>8</v>
+        <v>10.3</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" t="n">
-        <v>193</v>
+        <v>22.45</v>
       </c>
       <c r="V39" t="n">
-        <v>201</v>
+        <v>0.24</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X39" t="n">
-        <v>20.05</v>
+        <v>21.6661077559205</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.18552036199095</v>
+        <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>20.7855869620576</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>20.1786711448505</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -5277,56 +4961,47 @@
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>89</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>114</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>685</v>
+        <v>2093</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>86.0683245874211</v>
+        <v>84.1487284521003</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>29.0174471992653</v>
       </c>
       <c r="E40" t="n">
-        <v>21.484375</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>60</v>
+        <v>489.6</v>
       </c>
       <c r="I40" t="n">
-        <v>882</v>
+        <v>405.5</v>
       </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>217.9</v>
       </c>
       <c r="K40" t="n">
-        <v>153</v>
+        <v>1113</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -5335,10 +5010,10 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>153</v>
+        <v>15.1</v>
       </c>
       <c r="O40" t="n">
-        <v>49</v>
+        <v>15.1</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
@@ -5347,40 +5022,40 @@
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>23.95</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X40" t="n">
-        <v>19.8</v>
+        <v>22.9720679092787</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.255506607929515</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>20.690094219506</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>20.1186577456453</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5389,7 +5064,7 @@
         <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -5401,102 +5076,95 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>182</v>
+        <v>204</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2601</v>
+        <v>657</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>80.6226186402008</v>
+        <v>83.0759392349228</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>28.6501377410468</v>
       </c>
       <c r="E41" t="n">
-        <v>34.2403214024835</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G41" t="n">
         <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>60</v>
-      </c>
-      <c r="I41" t="inlineStr"/>
+        <v>819.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>99.09999999999999</v>
+      </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>237.1</v>
       </c>
       <c r="K41" t="n">
-        <v>377</v>
+        <v>1155.4</v>
       </c>
       <c r="L41" t="n">
-        <v>83</v>
+        <v>19.5</v>
       </c>
       <c r="M41" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>543</v>
+        <v>40.2</v>
       </c>
       <c r="O41" t="n">
-        <v>59</v>
+        <v>59.7</v>
       </c>
       <c r="P41" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>21.85</v>
       </c>
       <c r="V41" t="n">
-        <v>53</v>
+        <v>0.36</v>
       </c>
       <c r="W41" t="n">
-        <v>2</v>
+        <v>23.3002291825821</v>
       </c>
       <c r="X41" t="n">
-        <v>23.15</v>
+        <v>22.1454723050462</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.205426356589147</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>23.1410746116628</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>22.7940734179357</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
@@ -5511,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -5522,101 +5190,94 @@
       <c r="AI41" t="n">
         <v>0</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
+      <c r="AJ41" t="inlineStr"/>
       <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
+        <v>200</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>574</v>
+        <v>485</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>78.2242470910335</v>
+        <v>89.0005646817248</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>22.0385674931129</v>
       </c>
       <c r="E42" t="n">
-        <v>22.151022507021</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G42" t="n">
         <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>510</v>
       </c>
       <c r="I42" t="n">
-        <v>1320</v>
+        <v>296</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>359</v>
       </c>
       <c r="K42" t="n">
-        <v>368</v>
+        <v>1165</v>
       </c>
       <c r="L42" t="n">
-        <v>278</v>
+        <v>35</v>
       </c>
       <c r="M42" t="n">
-        <v>181.2</v>
+        <v>17</v>
       </c>
       <c r="N42" t="n">
-        <v>827.2</v>
+        <v>153</v>
       </c>
       <c r="O42" t="n">
-        <v>28.9</v>
+        <v>205</v>
       </c>
       <c r="P42" t="n">
-        <v>6.9</v>
+        <v>14</v>
       </c>
       <c r="Q42" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>96.8</v>
+        <v>232</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>246</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>73.40000000000001</v>
+        <v>22.05</v>
       </c>
       <c r="V42" t="n">
-        <v>73.40000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="W42" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X42" t="n">
-        <v>22.4</v>
+        <v>22.1655797488585</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.156378600823045</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>22.5362872421696</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>22.1627083737899</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -5637,111 +5298,102 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN42" t="inlineStr"/>
+        <v>138</v>
+      </c>
+      <c r="AK42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>696</v>
+        <v>576</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>78.7061113329277</v>
+        <v>80.5730949121606</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>26.2975778546712</v>
       </c>
       <c r="E43" t="n">
-        <v>28.1969212010364</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>60</v>
+        <v>483.4</v>
       </c>
       <c r="I43" t="n">
-        <v>4960</v>
+        <v>564.9</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>380.1</v>
       </c>
       <c r="K43" t="n">
-        <v>842.5</v>
+        <v>1428.4</v>
       </c>
       <c r="L43" t="n">
-        <v>476.1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>627.6</v>
+        <v>13.8</v>
       </c>
       <c r="N43" t="n">
-        <v>1946.2</v>
+        <v>19.1</v>
       </c>
       <c r="O43" t="n">
-        <v>110.9</v>
+        <v>32.90000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>79.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>219.1</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>409.9</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>57.7</v>
+        <v>26.35</v>
       </c>
       <c r="V43" t="n">
-        <v>97.09999999999999</v>
+        <v>0.2</v>
       </c>
       <c r="W43" t="n">
-        <v>2</v>
+        <v>26.5469824293354</v>
       </c>
       <c r="X43" t="n">
-        <v>24.3</v>
+        <v>26.0806653934161</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.206642066420664</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>24.2551566080978</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>23.9911309690755</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -5753,10 +5405,10 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH43" t="n">
         <v>0</v>
@@ -5765,24 +5417,15 @@
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN43" t="n">
         <v>166</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>573</v>
+        <v>746</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5790,79 +5433,79 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>74.9002794889345</v>
+        <v>77.1758883121657</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>33.203125</v>
       </c>
       <c r="E44" t="n">
-        <v>41.659990386156</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>60</v>
+        <v>323</v>
       </c>
       <c r="I44" t="n">
-        <v>854</v>
+        <v>172</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="K44" t="n">
-        <v>217.2</v>
+        <v>638</v>
       </c>
       <c r="L44" t="n">
-        <v>183.2</v>
+        <v>40</v>
       </c>
       <c r="M44" t="n">
-        <v>124.3</v>
+        <v>14</v>
       </c>
       <c r="N44" t="n">
-        <v>524.7</v>
+        <v>14</v>
       </c>
       <c r="O44" t="n">
-        <v>6.9</v>
+        <v>68</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>19.1</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>20.65</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>21.0720651897123</v>
       </c>
       <c r="X44" t="n">
-        <v>21.05</v>
+        <v>20.7723337439364</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.253112033195021</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>21.5495289024701</v>
+        <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>20.9523162086917</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -5877,114 +5520,107 @@
         <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="n">
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>591</v>
+        <v>898</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>75.4179690470758</v>
+        <v>79.69788897127791</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>22.2222222222222</v>
       </c>
       <c r="E45" t="n">
-        <v>34.220041322314</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>60</v>
-      </c>
-      <c r="I45" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="I45" t="n">
+        <v>74</v>
+      </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>71</v>
       </c>
       <c r="K45" t="n">
-        <v>378</v>
+        <v>236</v>
       </c>
       <c r="L45" t="n">
-        <v>398</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>340</v>
+        <v>5</v>
       </c>
       <c r="N45" t="n">
-        <v>1116</v>
+        <v>5</v>
       </c>
       <c r="O45" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="P45" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>22.2</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W45" t="n">
-        <v>1</v>
+        <v>21.9633307868602</v>
       </c>
       <c r="X45" t="n">
-        <v>27.2</v>
+        <v>21.9056486523839</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.155932203389831</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>26.7379679144385</v>
+        <v>1</v>
       </c>
       <c r="AA45" t="n">
-        <v>26.2896834807734</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6011,116 +5647,107 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK45" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>180</v>
+        <v>148</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>487</v>
+        <v>362</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>86.317406900398</v>
+        <v>78.7965795878013</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>30.2595039739538</v>
       </c>
       <c r="E46" t="n">
-        <v>16.5051903114186</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>471</v>
       </c>
       <c r="I46" t="n">
-        <v>6570</v>
+        <v>190</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>194</v>
       </c>
       <c r="K46" t="n">
-        <v>772</v>
+        <v>855</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="M46" t="n">
-        <v>244</v>
+        <v>24</v>
       </c>
       <c r="N46" t="n">
-        <v>1166</v>
+        <v>95</v>
       </c>
       <c r="O46" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Q46" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>223</v>
+        <v>17</v>
       </c>
       <c r="S46" t="n">
-        <v>158</v>
+        <v>37</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>24</v>
+        <v>26.65</v>
       </c>
       <c r="V46" t="n">
-        <v>182</v>
+        <v>0.25</v>
       </c>
       <c r="W46" t="n">
-        <v>1</v>
+        <v>28.0112044817927</v>
       </c>
       <c r="X46" t="n">
-        <v>25.45</v>
+        <v>26.4585955298766</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.32013201320132</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>27.1836007130125</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>26.0709028381822</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6135,146 +5762,130 @@
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>711</v>
+        <v>2020</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>no event</t>
+          <t>pacer</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>85.7972290351611</v>
+        <v>75.0263963989657</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>24.6913580246913</v>
       </c>
       <c r="E47" t="n">
-        <v>25.2825698988697</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G47" t="n">
         <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>45</v>
+        <v>696.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4550</v>
+        <v>124.3</v>
       </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>493</v>
+        <v>918.1999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>161</v>
+        <v>56.6</v>
       </c>
       <c r="M47" t="n">
-        <v>142</v>
+        <v>31</v>
       </c>
       <c r="N47" t="n">
-        <v>796</v>
+        <v>1.1</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>88.69999999999999</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>84</v>
+        <v>5.4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>27.2</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>0.31</v>
       </c>
       <c r="W47" t="n">
-        <v>1</v>
+        <v>28.0430353959766</v>
       </c>
       <c r="X47" t="n">
-        <v>24.4</v>
+        <v>27.1495243336942</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.108527131782946</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>24.5098039215686</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>24.3021352118366</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AK47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN47" t="inlineStr"/>
+        <v>236</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>622</v>
+        <v>555</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -6282,79 +5893,79 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>89.18695401424699</v>
+        <v>82.8866092478516</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>26.4235698242832</v>
       </c>
       <c r="E48" t="n">
-        <v>23.2525951557093</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
+        <v>236</v>
+      </c>
+      <c r="I48" t="n">
+        <v>300</v>
+      </c>
+      <c r="J48" t="n">
+        <v>165</v>
+      </c>
+      <c r="K48" t="n">
+        <v>701</v>
+      </c>
+      <c r="L48" t="n">
+        <v>16</v>
+      </c>
+      <c r="M48" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" t="n">
+        <v>29</v>
+      </c>
+      <c r="O48" t="n">
         <v>55</v>
       </c>
-      <c r="I48" t="n">
-        <v>2560</v>
-      </c>
-      <c r="J48" t="n">
-        <v>1</v>
-      </c>
-      <c r="K48" t="n">
-        <v>162</v>
-      </c>
-      <c r="L48" t="n">
-        <v>349</v>
-      </c>
-      <c r="M48" t="n">
-        <v>302</v>
-      </c>
-      <c r="N48" t="n">
-        <v>813</v>
-      </c>
-      <c r="O48" t="n">
-        <v>5</v>
-      </c>
       <c r="P48" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>23.3</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X48" t="n">
-        <v>27.45</v>
+        <v>23.1211849536588</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.257142857142857</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>27.6928953399542</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>26.8406888888731</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -6381,22 +5992,15 @@
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN48" t="inlineStr"/>
+        <v>170</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>321</v>
+        <v>2073</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -6404,80 +6008,82 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>79.8068831596826</v>
+        <v>86.328758302279</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>33.6326530612244</v>
       </c>
       <c r="E49" t="n">
-        <v>24.1684694429421</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>60</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>1095.3</v>
+      </c>
+      <c r="I49" t="n">
+        <v>600</v>
+      </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>673.8</v>
       </c>
       <c r="K49" t="n">
-        <v>281</v>
+        <v>2369.1</v>
       </c>
       <c r="L49" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>166</v>
+        <v>31.4</v>
       </c>
       <c r="N49" t="n">
-        <v>684</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>19</v>
+        <v>31.4</v>
       </c>
       <c r="P49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>30.35</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="W49" t="n">
-        <v>1</v>
+        <v>29.9847211611918</v>
       </c>
       <c r="X49" t="n">
-        <v>23.7</v>
+        <v>29.7211204525439</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.237918215613383</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>23.6652872775905</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6486,39 +6092,30 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>152</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>589</v>
+        <v>610</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -6526,79 +6123,79 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>78.96926572362921</v>
+        <v>80.4444026161685</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>38.7396694214876</v>
       </c>
       <c r="E50" t="n">
-        <v>27.7551020408163</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
+        <v>966</v>
       </c>
       <c r="I50" t="n">
-        <v>152</v>
+        <v>1037</v>
       </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>221</v>
       </c>
       <c r="K50" t="n">
-        <v>114</v>
+        <v>2224</v>
       </c>
       <c r="L50" t="n">
-        <v>154</v>
+        <v>18</v>
       </c>
       <c r="M50" t="n">
-        <v>132</v>
+        <v>17</v>
       </c>
       <c r="N50" t="n">
-        <v>400</v>
+        <v>18</v>
       </c>
       <c r="O50" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="P50" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>46</v>
+        <v>29.95</v>
       </c>
       <c r="V50" t="n">
-        <v>46</v>
+        <v>0.26</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>31.5126050420168</v>
       </c>
       <c r="X50" t="n">
-        <v>21.3</v>
+        <v>30.3986119121575</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.3359375</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>21.4357677787856</v>
+        <v>1</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
@@ -6610,125 +6207,114 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI50" t="n">
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>180</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="AK50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2001</v>
+        <v>632</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pacer</t>
+          <t>no event</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>78.18058825766219</v>
+        <v>72.13777473572139</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>28.0890109547142</v>
       </c>
       <c r="E51" t="n">
-        <v>30.078125</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>60</v>
+        <v>379</v>
       </c>
       <c r="I51" t="n">
-        <v>4400</v>
+        <v>491.8</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>284.9</v>
       </c>
       <c r="K51" t="n">
-        <v>180.1</v>
+        <v>1155.7</v>
       </c>
       <c r="L51" t="n">
-        <v>222.6</v>
+        <v>140.4</v>
       </c>
       <c r="M51" t="n">
-        <v>117.4</v>
+        <v>193.1</v>
       </c>
       <c r="N51" t="n">
-        <v>520.1</v>
+        <v>44</v>
       </c>
       <c r="O51" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="P51" t="n">
         <v>12.6</v>
       </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
       <c r="Q51" t="n">
-        <v>16.8</v>
+        <v>17.6</v>
       </c>
       <c r="R51" t="n">
-        <v>29.4</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>30.2</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>26.55</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>0.19</v>
       </c>
       <c r="W51" t="n">
-        <v>2</v>
+        <v>26.5151515151515</v>
       </c>
       <c r="X51" t="n">
-        <v>24.15</v>
+        <v>26.2096759585991</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.197761194029851</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>24.0005092946269</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>23.7029066974866</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
         <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>
@@ -6740,33 +6326,24 @@
         <v>0</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH51" t="n">
         <v>0</v>
       </c>
       <c r="AI51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>152</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2013</v>
+        <v>902</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6774,77 +6351,79 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>92.0309740284432</v>
+        <v>87.1663702246052</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>32.3883554336229</v>
       </c>
       <c r="E52" t="n">
-        <v>26.7949380165289</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
+        <v>75.7</v>
+      </c>
+      <c r="I52" t="n">
+        <v>61.6</v>
+      </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>26.8</v>
       </c>
       <c r="K52" t="n">
-        <v>262.3</v>
+        <v>164.1</v>
       </c>
       <c r="L52" t="n">
-        <v>377.1</v>
+        <v>8</v>
       </c>
       <c r="M52" t="n">
-        <v>280.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>919.7</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="P52" t="n">
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>29.1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>36.7</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>22.895</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X52" t="n">
-        <v>24.6</v>
+        <v>22.1942730679895</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.122137404580153</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>24.5098039215686</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>26.4561900936673</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
@@ -6862,150 +6441,249 @@
         <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN52" t="inlineStr"/>
+        <v>160</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>634</v>
+        <v>1698</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>pacer</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>87.9844727735949</v>
+      </c>
+      <c r="D53" t="n">
+        <v>30.1160023795359</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>50</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" t="n">
+        <v>282</v>
+      </c>
+      <c r="I53" t="n">
+        <v>487</v>
+      </c>
+      <c r="J53" t="n">
+        <v>571</v>
+      </c>
+      <c r="K53" t="n">
+        <v>1340</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>93</v>
+      </c>
+      <c r="N53" t="n">
+        <v>141</v>
+      </c>
+      <c r="O53" t="n">
+        <v>234</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>27.35</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W53" t="n">
+        <v>28.3295136236313</v>
+      </c>
+      <c r="X53" t="n">
+        <v>27.6120628833503</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>136</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>633</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>no event</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>85.36462278500269</v>
-      </c>
-      <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="n">
-        <v>30.4271978579252</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>45</v>
-      </c>
-      <c r="I53" t="n">
-        <v>2040</v>
-      </c>
-      <c r="J53" t="n">
-        <v>1</v>
-      </c>
-      <c r="K53" t="n">
-        <v>78</v>
-      </c>
-      <c r="L53" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
+      <c r="C54" t="n">
+        <v>82.8868868355008</v>
+      </c>
+      <c r="D54" t="n">
+        <v>37.4213957794838</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>30</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" t="n">
+        <v>187</v>
+      </c>
+      <c r="I54" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>165.6</v>
+      </c>
+      <c r="K54" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
         <v>2</v>
       </c>
-      <c r="X53" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>0.271698113207547</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>23.2365673542144</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>22.6736985933985</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>186</v>
+      <c r="U54" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="V54" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="W54" t="n">
+        <v>25.305576776165</v>
+      </c>
+      <c r="X54" t="n">
+        <v>24.856233988737</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>136</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
